--- a/processed-data/21_Xenium/13.1_xenium_compare_bansky_clusters/banksy_clustering_annotation_k11_summary.xlsx
+++ b/processed-data/21_Xenium/13.1_xenium_compare_bansky_clusters/banksy_clustering_annotation_k11_summary.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/21_Xenium/13.1_xenium_compare_bansky_clusters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{A3DE8289-B4D8-0B48-BA93-A1E439C2703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4432B382-F42C-EE4F-8CDE-D392F483CAE9}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{A3DE8289-B4D8-0B48-BA93-A1E439C2703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CD7A4D9-B516-0E4B-89EC-B70AC700ED38}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{76241F0D-2465-BD4B-8A74-F93DEE6FB35C}"/>
+    <workbookView xWindow="36060" yWindow="2280" windowWidth="22340" windowHeight="17180" xr2:uid="{76241F0D-2465-BD4B-8A74-F93DEE6FB35C}"/>
   </bookViews>
   <sheets>
     <sheet name="banksy_clustering_annotation_k1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">banksy_clustering_annotation_k1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">banksy_clustering_annotation_k1!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
   <si>
     <t>cluster</t>
   </si>
@@ -181,18 +181,9 @@
     <t>anno</t>
   </si>
   <si>
-    <t>Vasc.mural</t>
-  </si>
-  <si>
-    <t>Vasc.PVM</t>
-  </si>
-  <si>
     <t>GL</t>
   </si>
   <si>
-    <t>Vasc.endo</t>
-  </si>
-  <si>
     <t>L2</t>
   </si>
   <si>
@@ -205,9 +196,6 @@
     <t>WMd</t>
   </si>
   <si>
-    <t>Wmuf</t>
-  </si>
-  <si>
     <t>L6</t>
   </si>
   <si>
@@ -215,6 +203,115 @@
   </si>
   <si>
     <t>layer_order</t>
+  </si>
+  <si>
+    <t>specific_cell_types</t>
+  </si>
+  <si>
+    <t>concentrated_cell_types</t>
+  </si>
+  <si>
+    <t>specific_cell_types_broad</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Excit.L2_5.2 (72%), Excit.L5.1 (66%), Excit.L5_6_NP (53%), Inhib.Pvalb (44%), Inhib.Sst (33%)</t>
+  </si>
+  <si>
+    <t>Excit (31%)</t>
+  </si>
+  <si>
+    <t>Inhib.Pax6 (50%), Inhib.Vip (46%), Astro.1 (28%), Inhib.Lamp5_Lhx6 (27%), Excit.L5.2 (22%)</t>
+  </si>
+  <si>
+    <t>Astro (40%)</t>
+  </si>
+  <si>
+    <t>Oligo.3 (33%)</t>
+  </si>
+  <si>
+    <t>Oligo.3 (21%)</t>
+  </si>
+  <si>
+    <t>Oligo (54%)</t>
+  </si>
+  <si>
+    <t>Excit.L2 (32%)</t>
+  </si>
+  <si>
+    <t>Excit.L2 (67%), Excit.L5.2 (33%), OPC.1 (29%), Excit.L2_5.1 (28%), Inhib.Vip (25%)</t>
+  </si>
+  <si>
+    <t>Excit (40%)</t>
+  </si>
+  <si>
+    <t>Astro (34%)</t>
+  </si>
+  <si>
+    <t>Macro (79%), Vasc.VLMC (69%), Micro.1 (28%), Vasc.PC (25%)</t>
+  </si>
+  <si>
+    <t>Vasc (65%)</t>
+  </si>
+  <si>
+    <t>Astro.4 (51%), Micro.3 (21%), Micro.4 (21%)</t>
+  </si>
+  <si>
+    <t>Astro (47%)</t>
+  </si>
+  <si>
+    <t>Vasc.PC (47%), Vasc.Endo (36%)</t>
+  </si>
+  <si>
+    <t>Vasc.PC (45%), Vasc.Endo (30%), Vasc.VLMC (24%)</t>
+  </si>
+  <si>
+    <t>Vasc (92%)</t>
+  </si>
+  <si>
+    <t>Excit.L6b (85%), Excit.L6_CT (83%), Excit.L5_6_NP (29%), Astro.3 (24%)</t>
+  </si>
+  <si>
+    <t>Oligo (38%)</t>
+  </si>
+  <si>
+    <t>Oligo.2 (60%), Micro.1 (46%), Oligo.1 (42%), Oligo.5 (36%), Micro.3 (34%)</t>
+  </si>
+  <si>
+    <t>Oligo (77%)</t>
+  </si>
+  <si>
+    <t>Vasc.Endo (20%)</t>
+  </si>
+  <si>
+    <t>Vasc (39%)</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>WMuf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interspersed in GM layers </t>
+  </si>
+  <si>
+    <t>Vasc.adj</t>
+  </si>
+  <si>
+    <t>Vasc.im</t>
+  </si>
+  <si>
+    <t>Vasc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mural/pericyte layer - claude
+looks like main blood vessles to us </t>
+  </si>
+  <si>
+    <t>Perivascular immune niche'</t>
   </si>
 </sst>
 </file>
@@ -698,10 +795,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -759,6 +860,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1078,16 +1183,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F21F3F0-4FC5-8740-A805-08D3C0D80837}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="6.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="75.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.83203125" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="77" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1098,7 +1207,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1106,16 +1215,28 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>51</v>
       </c>
+      <c r="L1" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -1127,21 +1248,33 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>63</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>75</v>
+      </c>
+      <c r="I2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -1153,19 +1286,31 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
+        <v>80</v>
+      </c>
+      <c r="I3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1184,14 +1329,26 @@
       <c r="F4" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="1">
         <v>6</v>
       </c>
-      <c r="H4" t="s">
-        <v>55</v>
+      <c r="K4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1210,14 +1367,23 @@
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="H5" t="s">
-        <v>54</v>
+      <c r="K5" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1236,14 +1402,23 @@
       <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="H6" t="s">
-        <v>56</v>
+      <c r="K6" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -1262,14 +1437,23 @@
       <c r="F7" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="1">
         <v>4</v>
       </c>
-      <c r="H7" t="s">
-        <v>57</v>
+      <c r="K7" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1288,14 +1472,23 @@
       <c r="F8" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" s="1">
         <v>5</v>
       </c>
-      <c r="H8" t="s">
-        <v>58</v>
+      <c r="K8" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1314,14 +1507,23 @@
       <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="1">
         <v>7</v>
       </c>
-      <c r="H9" t="s">
-        <v>62</v>
+      <c r="K9" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1340,14 +1542,23 @@
       <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="1">
         <v>8</v>
       </c>
-      <c r="H10" t="s">
-        <v>61</v>
+      <c r="K10" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1366,14 +1577,23 @@
       <c r="F11" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="1">
         <v>9</v>
       </c>
-      <c r="H11" t="s">
-        <v>60</v>
+      <c r="K11" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1392,16 +1612,25 @@
       <c r="F12" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="1">
         <v>10</v>
       </c>
-      <c r="H12" t="s">
-        <v>59</v>
+      <c r="K12" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{2F21F3F0-4FC5-8740-A805-08D3C0D80837}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H12">
+  <autoFilter ref="A1:L1" xr:uid="{2F21F3F0-4FC5-8740-A805-08D3C0D80837}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L12">
       <sortCondition ref="D1:D12"/>
     </sortState>
   </autoFilter>

--- a/processed-data/21_Xenium/13.1_xenium_compare_bansky_clusters/banksy_clustering_annotation_k11_summary.xlsx
+++ b/processed-data/21_Xenium/13.1_xenium_compare_bansky_clusters/banksy_clustering_annotation_k11_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/21_Xenium/13.1_xenium_compare_bansky_clusters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="8_{A3DE8289-B4D8-0B48-BA93-A1E439C2703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CD7A4D9-B516-0E4B-89EC-B70AC700ED38}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{A3DE8289-B4D8-0B48-BA93-A1E439C2703E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DACB192-08BE-DE40-BBA4-EC33BDDB0AF6}"/>
   <bookViews>
-    <workbookView xWindow="36060" yWindow="2280" windowWidth="22340" windowHeight="17180" xr2:uid="{76241F0D-2465-BD4B-8A74-F93DEE6FB35C}"/>
+    <workbookView xWindow="36060" yWindow="2280" windowWidth="32480" windowHeight="17180" xr2:uid="{76241F0D-2465-BD4B-8A74-F93DEE6FB35C}"/>
   </bookViews>
   <sheets>
     <sheet name="banksy_clustering_annotation_k1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="97">
   <si>
     <t>cluster</t>
   </si>
@@ -187,12 +187,6 @@
     <t>L2</t>
   </si>
   <si>
-    <t>Inhib</t>
-  </si>
-  <si>
-    <t>LD</t>
-  </si>
-  <si>
     <t>WMd</t>
   </si>
   <si>
@@ -298,20 +292,29 @@
     <t xml:space="preserve">interspersed in GM layers </t>
   </si>
   <si>
-    <t>Vasc.adj</t>
-  </si>
-  <si>
-    <t>Vasc.im</t>
-  </si>
-  <si>
-    <t>Vasc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mural/pericyte layer - claude
+    <t>Perivascular immune niche'</t>
+  </si>
+  <si>
+    <t>Vasc_im</t>
+  </si>
+  <si>
+    <t>Vasc_mural</t>
+  </si>
+  <si>
+    <t>Vasc_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mural/pericyte layer
 looks like main blood vessles to us </t>
   </si>
   <si>
-    <t>Perivascular immune niche'</t>
+    <t>LD_glia</t>
+  </si>
+  <si>
+    <t>L1_inhib</t>
+  </si>
+  <si>
+    <t>Layer 1 position + Inhib.Pax6, VIP, and Lamp5 enrichment</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1210,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1216,13 +1219,13 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" t="s">
-        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>50</v>
@@ -1231,7 +1234,7 @@
         <v>51</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1254,22 +1257,22 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="51" x14ac:dyDescent="0.2">
@@ -1292,22 +1295,22 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" t="s">
         <v>79</v>
-      </c>
-      <c r="H3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s">
-        <v>81</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -1330,22 +1333,22 @@
         <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J4" s="1">
         <v>6</v>
       </c>
       <c r="K4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1368,13 +1371,13 @@
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J5" s="1">
         <v>2</v>
@@ -1385,72 +1388,75 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>95</v>
+      </c>
+      <c r="L6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1473,19 +1479,19 @@
         <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1508,19 +1514,19 @@
         <v>32</v>
       </c>
       <c r="G9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" t="s">
         <v>63</v>
-      </c>
-      <c r="H9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" t="s">
-        <v>65</v>
       </c>
       <c r="J9" s="1">
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1543,19 +1549,19 @@
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J10" s="1">
         <v>8</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1578,19 +1584,19 @@
         <v>24</v>
       </c>
       <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" t="s">
-        <v>70</v>
       </c>
       <c r="J11" s="1">
         <v>9</v>
       </c>
       <c r="K11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1613,19 +1619,19 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
       </c>
       <c r="K12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
